--- a/data/trans_orig/IP19C01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C01-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36070</t>
+          <t>36583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46513</t>
+          <t>46628</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33535</t>
+          <t>33580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43010</t>
+          <t>42954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73289</t>
+          <t>73504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87627</t>
+          <t>87216</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18725</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>16936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>30648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21080</t>
+          <t>22278</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>32465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19878</t>
+          <t>19426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29254</t>
+          <t>29337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45572</t>
+          <t>45300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58577</t>
+          <t>59058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>76,16%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>18220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>17620</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18967</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31972</t>
+          <t>32244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,58%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27586</t>
+          <t>27523</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43604</t>
+          <t>42963</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55138</t>
+          <t>54928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68853</t>
+          <t>68383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>19996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33241</t>
+          <t>33451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63525</t>
+          <t>62755</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77650</t>
+          <t>77300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63608</t>
+          <t>62698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76648</t>
+          <t>76895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>130105</t>
+          <t>130466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150922</t>
+          <t>150306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20487</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>35382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19506</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32546</t>
+          <t>33456</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43369</t>
+          <t>43985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64186</t>
+          <t>63825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>24628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36285</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41228</t>
+          <t>41480</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53202</t>
+          <t>53769</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>68711</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86827</t>
+          <t>85773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>18376</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16833</t>
+          <t>16266</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28807</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37866</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55807</t>
+          <t>55982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>19001</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28749</t>
+          <t>28827</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23293</t>
+          <t>23128</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>31117</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44855</t>
+          <t>44703</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57495</t>
+          <t>57631</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>20999</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18232</t>
+          <t>18096</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30872</t>
+          <t>31024</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>202922</t>
+          <t>202719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>230933</t>
+          <t>231756</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235957</t>
+          <t>234759</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>260534</t>
+          <t>262521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>446943</t>
+          <t>447790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>484071</t>
+          <t>484070</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92165</t>
+          <t>91342</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120176</t>
+          <t>120379</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81154</t>
+          <t>79167</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105731</t>
+          <t>106929</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>180715</t>
+          <t>180716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217843</t>
+          <t>216996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29669</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>40483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26989</t>
+          <t>27365</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35567</t>
+          <t>35583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59815</t>
+          <t>60041</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73635</t>
+          <t>73655</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>19892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30065</t>
+          <t>29839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40301</t>
+          <t>40377</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33081</t>
+          <t>34420</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44546</t>
+          <t>44755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67735</t>
+          <t>67375</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81878</t>
+          <t>81698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18183</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19228</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33371</t>
+          <t>33731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27888</t>
+          <t>28001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36838</t>
+          <t>36911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24314</t>
+          <t>24331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33694</t>
+          <t>33657</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55513</t>
+          <t>56595</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68117</t>
+          <t>68915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>14460</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27356</t>
+          <t>26274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58430</t>
+          <t>58371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72233</t>
+          <t>72190</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68258</t>
+          <t>69442</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81911</t>
+          <t>82198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131116</t>
+          <t>130404</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150686</t>
+          <t>150442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,52%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18995</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32798</t>
+          <t>32857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16055</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29708</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38509</t>
+          <t>38753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58079</t>
+          <t>58791</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45994</t>
+          <t>45804</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59591</t>
+          <t>60193</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41483</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>54900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92111</t>
+          <t>91880</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111798</t>
+          <t>111581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22637</t>
+          <t>22035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36234</t>
+          <t>36424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18287</t>
+          <t>18767</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32184</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44097</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63784</t>
+          <t>64015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,06%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23069</t>
+          <t>23075</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26704</t>
+          <t>27058</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34305</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46248</t>
+          <t>46159</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55969</t>
+          <t>56118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228502</t>
+          <t>228337</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>256341</t>
+          <t>255335</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>243955</t>
+          <t>243964</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>270474</t>
+          <t>270248</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>482226</t>
+          <t>479693</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>520024</t>
+          <t>518529</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82294</t>
+          <t>83300</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110133</t>
+          <t>110298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73041</t>
+          <t>73267</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>99560</t>
+          <t>99551</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>162126</t>
+          <t>163621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>199924</t>
+          <t>202457</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>26839</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>36830</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39024</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>58909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73687</t>
+          <t>73190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,25%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11490</t>
+          <t>11795</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>22834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>20343</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34430</t>
+          <t>34624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39087</t>
+          <t>39892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49616</t>
+          <t>49316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36029</t>
+          <t>36794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46270</t>
+          <t>46231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78886</t>
+          <t>79849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93295</t>
+          <t>93218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>15842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18001</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>16546</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30878</t>
+          <t>29915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20515</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>28131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24671</t>
+          <t>24952</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>32031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48567</t>
+          <t>48663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58574</t>
+          <t>58562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18288</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70952</t>
+          <t>71478</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86175</t>
+          <t>86767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72228</t>
+          <t>71747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86431</t>
+          <t>86831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147575</t>
+          <t>147906</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>168747</t>
+          <t>168078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>25057</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>40346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33021</t>
+          <t>33502</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48326</t>
+          <t>48995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69498</t>
+          <t>69167</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37626</t>
+          <t>37924</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50785</t>
+          <t>51256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52343</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>64304</t>
+          <t>64171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93770</t>
+          <t>92979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111538</t>
+          <t>111654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32440</t>
+          <t>32142</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21835</t>
+          <t>21951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32706</t>
+          <t>32590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50474</t>
+          <t>51265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20024</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28282</t>
+          <t>28189</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>26962</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40609</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53020</t>
+          <t>52849</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,62%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>12192</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>14948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12705</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>237412</t>
+          <t>235980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>263591</t>
+          <t>262704</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>252745</t>
+          <t>253404</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>278509</t>
+          <t>279682</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>497066</t>
+          <t>496942</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>535407</t>
+          <t>537207</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81558</t>
+          <t>82445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>107737</t>
+          <t>109169</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73365</t>
+          <t>72192</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>99129</t>
+          <t>98470</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>161616</t>
+          <t>159816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>199957</t>
+          <t>200081</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,71%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47446</t>
+          <t>47617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60536</t>
+          <t>60556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75316</t>
+          <t>76199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87964</t>
+          <t>88589</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127185</t>
+          <t>126336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145679</t>
+          <t>145187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20774</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>22677</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40679</t>
+          <t>41528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>46206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56549</t>
+          <t>56773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56823</t>
+          <t>57196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66955</t>
+          <t>66376</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>107250</t>
+          <t>106720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121837</t>
+          <t>121419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16340</t>
+          <t>16495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>12870</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16137</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24219</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29516</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52261</t>
+          <t>51865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17015</t>
+          <t>16997</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11927</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25736</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86536</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100298</t>
+          <t>100374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84018</t>
+          <t>84225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105198</t>
+          <t>105431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176530</t>
+          <t>176846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>201647</t>
+          <t>200789</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,21%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22195</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43375</t>
+          <t>43168</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>37650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61909</t>
+          <t>61593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>45182</t>
+          <t>44627</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60370</t>
+          <t>60291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>79812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96781</t>
+          <t>96565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130775</t>
+          <t>131442</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154472</t>
+          <t>153934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23316</t>
+          <t>23871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23284</t>
+          <t>23388</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40923</t>
+          <t>40256</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41594</t>
+          <t>41409</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32145</t>
+          <t>32273</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42137</t>
+          <t>41476</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69171</t>
+          <t>68276</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81647</t>
+          <t>81329</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7670</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19828</t>
+          <t>20723</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>297347</t>
+          <t>299245</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>327523</t>
+          <t>328047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>374287</t>
+          <t>376745</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>409297</t>
+          <t>410032</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>685091</t>
+          <t>686202</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>729148</t>
+          <t>729860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59290</t>
+          <t>58766</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>89466</t>
+          <t>87568</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>69368</t>
+          <t>68633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104378</t>
+          <t>101920</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>136330</t>
+          <t>135618</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>180387</t>
+          <t>179276</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
